--- a/docs/evidence/20261024_Azure實付價_A段/Azure實付價_A段.xlsx
+++ b/docs/evidence/20261024_Azure實付價_A段/Azure實付價_A段.xlsx
@@ -1733,7 +1733,45 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">」；以下用『每顆』讀法，因為 </t>
+      <t xml:space="preserve">」；以下用『每顆』讀法：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">The Information </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">原句寫 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">chips</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">；若 </t>
     </r>
     <r>
       <rPr>
@@ -1752,6 +1790,139 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
+      <t xml:space="preserve">萬是 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">8 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">顆伺服器，則 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">280 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">萬顆 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">A100 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">約 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2.6 GW</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">，遠超 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">OpenAI 2024 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">年底總量 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">0.6 GW</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">。金額 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">35 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
       <t xml:space="preserve">萬</t>
     </r>
     <r>
@@ -1771,7 +1942,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">＝約 </t>
+      <t xml:space="preserve">＝</t>
     </r>
     <r>
       <rPr>
@@ -1790,64 +1961,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">億與同文『約 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">40 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">億』吻合，若指整台 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">8 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">顆伺服器則每顆僅 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">0.16 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">美元、金額對不上</t>
+      <t xml:space="preserve">億兩種讀法都吻合</t>
     </r>
   </si>
   <si>

--- a/docs/evidence/20261024_Azure實付價_A段/Azure實付價_A段.xlsx
+++ b/docs/evidence/20261024_Azure實付價_A段/Azure實付價_A段.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="698" uniqueCount="454">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="702" uniqueCount="456">
   <si>
     <t xml:space="preserve">名稱</t>
   </si>
@@ -9114,54 +9114,73 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">1.45 GW → </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">證偽條件 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(a)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">（≥</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">1.8</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">）不可能由端點資料成立</t>
+      <t xml:space="preserve">1.45 GW</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">；要達 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1.8 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">須約 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">4 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">週內到位 → 證偽條件 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(a) </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">不可能由端點資料成立</t>
     </r>
   </si>
   <si>
@@ -10326,6 +10345,209 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
+      <t xml:space="preserve">上限 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">217 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">億（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">s</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">＝</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）：所需最低倍數（前重上限 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">GW</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">s</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">＝</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">0.79 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">即 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">161÷204</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">，與支出下限共線，非獨立假設；全部供應商總支出</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">÷</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">總 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">GW → </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">為跨供應商混合倍數，非 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Azure </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">單價</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
       <t xml:space="preserve">線性內插 </t>
     </r>
     <r>
@@ -11169,7 +11391,207 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">內；世代與年度不同</t>
+      <t xml:space="preserve">內；世代與年度不同。單位未證實：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">DCD </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">原文為 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">$1.30 per A100 server per hour</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">350,000 servers</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">；</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Willison </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">轉引 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">The Information </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">為 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">350,000 A100 chips</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">；本段採『每顆』是依容量推論（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">8 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">顆／台會得 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2.6 GW</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">＞</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">0.6 GW</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">），原文單位未證實。若真為每台，實付約低至 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">0.16 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">倍，更傾向觸發證偽 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(b)</t>
     </r>
   </si>
   <si>
@@ -12871,7 +13293,83 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">支持（偏高端）：最低 </t>
+      <t xml:space="preserve">弱支持（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2027 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">起未來價、非 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Azure</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">facility </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">與爬坡為 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Assumed</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）：最低 </t>
     </r>
     <r>
       <rPr>
@@ -12890,7 +13388,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">，合理 </t>
+      <t xml:space="preserve">，基準 </t>
     </r>
     <r>
       <rPr>
@@ -12909,26 +13407,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">，</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">facility</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">＋爬坡可達 </t>
+      <t xml:space="preserve">，高 </t>
     </r>
     <r>
       <rPr>
@@ -12940,15 +13419,6 @@
       </rPr>
       <t xml:space="preserve">3.1</t>
     </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">；但屬未來價</t>
-    </r>
   </si>
   <si>
     <t xml:space="preserve">E06</t>
@@ -13305,17 +13775,639 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">弱反對：純供應商毛利只能解釋 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">1.19–1.67 </t>
+      <t xml:space="preserve">單列對照（不併入 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1.0–1.5 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">群）：價格</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">÷</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">供應商會計 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">COGS</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">，與『</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">÷TK </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">持有成本』口徑不同；純毛利只對應 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1.19–1.67</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">E07</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">S6 CoreWeave </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">申報</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">CoreWeave </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">營收</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">÷</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">活躍電力</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">CoreWeave 2025Q4 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">新聞稿 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">https://www.businesswire.com/news/home/20260226281661/en/CoreWeave-Reports-Strong-Fourth-Quarter-and-Fiscal-Year-2025-Results</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">；</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Q3 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">稿（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">9a</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2026-02-26</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">／讀取 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2026-10-24</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Q4 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">營收 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1,572 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">百萬；</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">'Added approximately 260 MW of active power capacity, bringing the total to more than 850 MW'</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Q3 1.365B</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">／</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">530MW</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">；</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Q4 1.572B</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">／</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">720MW</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">全客戶、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Hopper </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">為主、含網路儲存；活躍電力口徑未明</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">年化營收</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">÷</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">平均活躍電力</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Verified</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（原數）／</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Derived</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（比值）；</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Analogy</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（非 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">OpenAI</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">、非 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Azure</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）；</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">active power </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">公司未定義，</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Q4 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">用『</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">more than 850 MW</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">』使倍數略高</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">反對：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">neocloud </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">已實現單價約 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">0.9–1.1 </t>
     </r>
     <r>
       <rPr>
@@ -13334,6 +14426,573 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
+      <t xml:space="preserve">Azure </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">對 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">OpenAI </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">若遠高於此需另有理由</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">E08</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">S7 IREN </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">公告</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Microsoft </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">向 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">IREN </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">租 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">GB300</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">techinformed </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">轉述 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">IREN </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">公告 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">https://techinformed.com/microsoft-signs-9-7-billion-iren-deal-for-nvidia-gb300-capacity/</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2025-11</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">／讀取 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2026-10-24</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">'about $9.7 billion'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">；五年；</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">'about 200 MW of IT load'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">；</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">20% </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">預付</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">97 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">億／</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">5 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">年／</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">200 MW IT</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">IT </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">口徑、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">GB300</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Microsoft </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">是買方</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">9.7÷5÷0.2</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Derived</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（金額為 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Verified</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+ Analogy</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（買方價，非賣給 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">OpenAI</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）；未處理 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">200 MW </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">分批爬坡，倍數偏低</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">反對（弱）：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Microsoft </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">向 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">neocloud </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">租的成本約 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1.0 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">倍；</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Azure </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">轉售給 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">OpenAI </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">要加到 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
       <t xml:space="preserve">1.8 </t>
     </r>
     <r>
@@ -13343,140 +15002,112 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">還需 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">TK </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">持有成本低估或隨需溢價（見 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">README</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">）</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">E07</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">S6 CoreWeave </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">申報</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">CoreWeave </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">營收</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">÷</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">活躍電力</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">CoreWeave 2025Q4 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">新聞稿 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">https://www.businesswire.com/news/home/20260226281661/en/CoreWeave-Reports-Strong-Fourth-Quarter-and-Fiscal-Year-2025-Results</t>
+      <t xml:space="preserve">倍需加價約 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">73%</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">E10</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">S8 Azure </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">牌價</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Azure ND H100 v5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">／</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">ND GB200 v6 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">公開牌價</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">azurespeed https://www.azurespeed.com/AzureVmPricing/Standard_ND96isr_H100_v5 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">、…</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">/Standard_ND128isr_NDR_GB200_v6</t>
     </r>
     <r>
       <rPr>
@@ -13495,47 +15126,104 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">Q3 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">稿（</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">9a</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">）</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">2026-02-26</t>
+      <t xml:space="preserve">sparecores</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">；</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">devzero</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">；</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Microsoft Learn</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">GB200 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">每 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">VM 4 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">顆）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2026</t>
     </r>
     <r>
       <rPr>
@@ -13566,76 +15254,121 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">Q4 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">營收 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">1,572 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">百萬；</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">'Added approximately 260 MW of active power capacity, bringing the total to more than 850 MW'</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Q3 1.365B</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">／</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">530MW</t>
+      <t xml:space="preserve">H100 v5 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">隨需 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">98.32 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">美元／小時（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">8 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">顆）；</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">GB200 v6 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">隨需 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">108.16</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">4 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">顆）、一年預留 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">69.222</t>
     </r>
     <r>
       <rPr>
@@ -13654,86 +15387,202 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">Q4 1.572B</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">／</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">720MW</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">全客戶、</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Hopper </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">為主、含網路儲存；活躍電力口徑未明</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">年化營收</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">÷</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">平均活躍電力</t>
+      <t xml:space="preserve">H100 Spot 18.1695</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">H100 12.29</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">／顆；</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">GB200 27.04</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">／顆</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">公開牌價（非 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">OpenAI </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">實付）；東美最低區</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">價</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">×</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">每 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">GW </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">顆數</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">×8760</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（基準欄＝</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">H100 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">三年預留；低＝</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">H100 Spot</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">；高＝</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">GB200 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">隨需）</t>
     </r>
   </si>
   <si>
@@ -13754,1280 +15603,6 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">（原數）／</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Derived</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">（比值）；</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Analogy</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">（非 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">OpenAI</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">、非 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Azure</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">）</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">反對：</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">neocloud </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">已實現單價約 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">0.9–1.1 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">倍；</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Azure </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">對 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">OpenAI </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">若遠高於此需另有理由</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">E08</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">S7 IREN </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">公告</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Microsoft </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">向 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">IREN </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">租 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">GB300</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">techinformed </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">轉述 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">IREN </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">公告 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">https://techinformed.com/microsoft-signs-9-7-billion-iren-deal-for-nvidia-gb300-capacity/</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">2025-11</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">／讀取 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">2026-10-24</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">'about $9.7 billion'</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">；五年；</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">'about 200 MW of IT load'</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">；</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">20% </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">預付</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">97 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">億／</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">5 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">年／</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">200 MW IT</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">IT </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">口徑、</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">GB300</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">、</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Microsoft </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">是買方</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">9.7÷5÷0.2</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Verified</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">（公司公告）</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">+ Analogy</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">（買方價，非賣給 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">OpenAI</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">）</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">反對（弱）：</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Microsoft </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">向 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">neocloud </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">租的成本約 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">1.0 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">倍；</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Azure </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">轉售給 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">OpenAI </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">要加到 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">1.8 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">倍需加價約 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">73%</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">E10</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">S8 Azure </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">牌價</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Azure ND H100 v5</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">／</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">ND GB200 v6 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">公開牌價</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">azurespeed https://www.azurespeed.com/AzureVmPricing/Standard_ND96isr_H100_v5 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">、…</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">/Standard_ND128isr_NDR_GB200_v6</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">；</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">sparecores</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">；</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">devzero</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">；</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Microsoft Learn</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">（</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">GB200 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">每 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">VM 4 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">顆）</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">2026</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">／讀取 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">2026-10-24</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">H100 v5 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">隨需 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">98.32 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">美元／小時（</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">8 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">顆）；</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">GB200 v6 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">隨需 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">108.16</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">（</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">4 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">顆）、一年預留 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">69.222</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">；</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">H100 Spot 18.1695</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">H100 12.29</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">／顆；</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">GB200 27.04</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">／顆</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">公開牌價（非 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">OpenAI </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">實付）；東美最低區</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">價</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">×</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">每 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">GW </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">顆數</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">×8760</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">（基準欄＝</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">H100 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">三年預留；低＝</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">H100 Spot</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">；高＝</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">GB200 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">隨需）</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Verified</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
       <t xml:space="preserve">（牌價）；非實付價</t>
     </r>
   </si>
@@ -15039,7 +15614,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">支持（上界）：牌價約 </t>
+      <t xml:space="preserve">無關（僅上界）：牌價非實付；</t>
     </r>
     <r>
       <rPr>
@@ -18522,7 +19097,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:E149"/>
+  <dimension ref="A1:E150"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="78"/>
@@ -20527,13 +21102,31 @@
         <v>260</v>
       </c>
       <c r="B149" s="0" t="n">
+        <f aca="false">參數!$D$9/參數!$B$2/換算!$B$133</f>
+        <v>1.60559292396696</v>
+      </c>
+      <c r="C149" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="D149" s="0" t="s">
+        <v>13</v>
+      </c>
+      <c r="E149" s="0" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="150" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A150" s="1" t="s">
+        <v>262</v>
+      </c>
+      <c r="B150" s="0" t="n">
         <f aca="false">換算!$B$136*參數!$D$10/換算!$B$124</f>
         <v>1.7448725608368</v>
       </c>
-      <c r="C149" s="0" t="s">
+      <c r="C150" s="0" t="s">
         <v>12</v>
       </c>
-      <c r="D149" s="0" t="s">
+      <c r="D150" s="0" t="s">
         <v>13</v>
       </c>
     </row>
@@ -20572,78 +21165,78 @@
   <sheetData>
     <row r="1" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="7" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="D1" s="7" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="E1" s="7" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="F1" s="7" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="G1" s="7" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="H1" s="7" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="I1" s="7" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="J1" s="7" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="K1" s="8" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="L1" s="7" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="M1" s="7" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="N1" s="7" t="s">
         <v>5</v>
       </c>
       <c r="O1" s="7" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="73.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" customFormat="false" ht="111.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="9" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="G2" s="9" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="H2" s="9" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="I2" s="9" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="J2" s="10" t="n">
         <f aca="false">換算!$B$14</f>
@@ -20662,39 +21255,39 @@
         <v>1.5219522612446</v>
       </c>
       <c r="N2" s="9" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="O2" s="11" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="9" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="B3" s="9" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="C3" s="11" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="D3" s="11" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="E3" s="9" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="F3" s="11" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="G3" s="9" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="H3" s="11" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="I3" s="11" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="J3" s="10"/>
       <c r="K3" s="10" t="n">
@@ -20704,39 +21297,39 @@
       <c r="L3" s="10"/>
       <c r="M3" s="10"/>
       <c r="N3" s="9" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="O3" s="11" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="9" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="E4" s="9" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="F4" s="9" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="G4" s="9" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="H4" s="9" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="I4" s="11" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="J4" s="10" t="n">
         <f aca="false">換算!$B$35/換算!$B$37</f>
@@ -20755,78 +21348,78 @@
         <v>2.25593204863091</v>
       </c>
       <c r="N4" s="9" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="O4" s="11" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="44" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="9" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="D5" s="9" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="E5" s="9" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="F5" s="9" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="G5" s="9" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="H5" s="11" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="I5" s="11" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="J5" s="10"/>
       <c r="K5" s="10"/>
       <c r="L5" s="10"/>
       <c r="M5" s="10"/>
       <c r="N5" s="9" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="O5" s="11" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="59.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="9" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="D6" s="9" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="E6" s="9" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="F6" s="9" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="G6" s="9" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="H6" s="9" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="I6" s="9" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="J6" s="10" t="n">
         <f aca="false">換算!$B$52</f>
@@ -20845,39 +21438,39 @@
         <v>3.08869053525032</v>
       </c>
       <c r="N6" s="9" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="O6" s="11" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="73.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="9" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="E7" s="9" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="F7" s="9" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="G7" s="9" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="H7" s="11" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="I7" s="9" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="J7" s="10"/>
       <c r="K7" s="10" t="n">
@@ -20893,39 +21486,39 @@
         <v>1.66666666666667</v>
       </c>
       <c r="N7" s="9" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="O7" s="11" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="59.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="9" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="D8" s="9" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="E8" s="9" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="F8" s="9" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="G8" s="9" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="H8" s="11" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="I8" s="11" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="J8" s="10" t="n">
         <f aca="false">換算!$B$76</f>
@@ -20944,39 +21537,39 @@
         <v>1.10143870030625</v>
       </c>
       <c r="N8" s="9" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="O8" s="11" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="44" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="9" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="D9" s="9" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="E9" s="9" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="F9" s="9" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="G9" s="9" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="H9" s="9" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="I9" s="9" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="J9" s="10" t="n">
         <f aca="false">換算!$B$85</f>
@@ -20992,39 +21585,39 @@
       </c>
       <c r="M9" s="10"/>
       <c r="N9" s="9" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="O9" s="11" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="88.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="9" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="D10" s="9" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="E10" s="9" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="F10" s="9" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="G10" s="9" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="H10" s="11" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="I10" s="11" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="J10" s="10" t="n">
         <f aca="false">換算!$B$98</f>
@@ -21043,39 +21636,39 @@
         <v>12.7074179185438</v>
       </c>
       <c r="N10" s="9" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="O10" s="11" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="55.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="9" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="C11" s="9" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="D11" s="9" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="E11" s="9" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="F11" s="9" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="G11" s="9" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="H11" s="11" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="I11" s="9" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="J11" s="10"/>
       <c r="K11" s="10" t="n">
@@ -21091,49 +21684,49 @@
         <v>1.45613647470354</v>
       </c>
       <c r="N11" s="9" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="O11" s="11" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="9" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="C12" s="9" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="D12" s="9" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="E12" s="9" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="F12" s="9" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="G12" s="11" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="H12" s="11" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="I12" s="11" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="J12" s="10"/>
       <c r="K12" s="10"/>
       <c r="L12" s="10"/>
       <c r="M12" s="10"/>
       <c r="N12" s="9" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="O12" s="11" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
     </row>
   </sheetData>
@@ -21164,257 +21757,257 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="5" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="9" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="B2" s="11" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="E2" s="11" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="9" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="B3" s="11" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="D3" s="9" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="E3" s="11" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="9" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="E4" s="11" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="9" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="D5" s="9" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="E5" s="11" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="9" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="D6" s="9" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="E6" s="11" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="9" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="E7" s="9" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="9" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="D8" s="9" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="E8" s="11" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="9" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="D9" s="9" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="E9" s="11" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="9" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="B10" s="11" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="D10" s="9" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="E10" s="11" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="9" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="C11" s="9" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="D11" s="9" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="E11" s="11" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="9" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="B12" s="11" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="C12" s="9" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="D12" s="9" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="E12" s="11" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="9" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="B13" s="11" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="C13" s="9" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="D13" s="9" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="E13" s="9" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="9" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="B14" s="11" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="C14" s="9" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="D14" s="9" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="E14" s="11" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="9" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="B15" s="11" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="C15" s="9" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="D15" s="9" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="E15" s="11" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
     </row>
   </sheetData>
